--- a/output/yearly_benthic_cover_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_83_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.65289530729438</v>
+        <v>45.59827330284922</v>
       </c>
       <c r="M2" t="n">
-        <v>99.38958786728165</v>
+        <v>100.058567484908</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.12716696758059</v>
+        <v>87.91679806951458</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96160755072682</v>
+        <v>45.85056609033798</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228961566200911</v>
+        <v>2.228506117191486</v>
       </c>
       <c r="E3" t="n">
-        <v>5.730662835385275</v>
+        <v>5.655795340565724</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429871887336369</v>
+        <v>0.7428353723971621</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98349538942169</v>
+        <v>33.94714109026675</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17741068174729</v>
+        <v>34.17042713026945</v>
       </c>
       <c r="I3" t="n">
-        <v>6.61997937650657</v>
+        <v>6.529371941341743</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64366992958523</v>
+        <v>4.642721077482263</v>
       </c>
       <c r="K3" t="n">
-        <v>11.87283303241939</v>
+        <v>12.0832019304854</v>
       </c>
       <c r="L3" t="n">
-        <v>48.92796072598754</v>
+        <v>48.83183739920319</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7624013091338</v>
+        <v>106.7656054200266</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.42379974002824</v>
+        <v>86.99932513121749</v>
       </c>
       <c r="C4" t="n">
-        <v>42.90218133225951</v>
+        <v>42.56366219619926</v>
       </c>
       <c r="D4" t="n">
-        <v>2.19620240432983</v>
+        <v>2.184182614409089</v>
       </c>
       <c r="E4" t="n">
-        <v>6.567818612800363</v>
+        <v>6.452057067312645</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744553291458022</v>
+        <v>0.7443872302507726</v>
       </c>
       <c r="G4" t="n">
-        <v>33.48403822367762</v>
+        <v>33.27195505826018</v>
       </c>
       <c r="H4" t="n">
-        <v>34.249451407069</v>
+        <v>34.24181259153553</v>
       </c>
       <c r="I4" t="n">
-        <v>5.528277729080765</v>
+        <v>5.452510380381938</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653458071612636</v>
+        <v>4.652420189067328</v>
       </c>
       <c r="K4" t="n">
-        <v>12.57620025997175</v>
+        <v>13.00067486878251</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33773009175466</v>
+        <v>44.25429149220317</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81611168398592</v>
+        <v>99.81862855718494</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.52295082352865</v>
+        <v>85.71100294647913</v>
       </c>
       <c r="C5" t="n">
-        <v>42.85957996702744</v>
+        <v>42.12155289388072</v>
       </c>
       <c r="D5" t="n">
-        <v>2.153194663842727</v>
+        <v>2.120785098149089</v>
       </c>
       <c r="E5" t="n">
-        <v>7.208384005238655</v>
+        <v>7.023415016174906</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458770942723333</v>
+        <v>0.7457049542379405</v>
       </c>
       <c r="G5" t="n">
-        <v>32.82832779209578</v>
+        <v>32.30621194782036</v>
       </c>
       <c r="H5" t="n">
-        <v>34.31034633652732</v>
+        <v>34.30242789494525</v>
       </c>
       <c r="I5" t="n">
-        <v>4.615089092349737</v>
+        <v>4.551802071164457</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661731839202083</v>
+        <v>4.660655963987128</v>
       </c>
       <c r="K5" t="n">
-        <v>13.47704917647136</v>
+        <v>14.28899705352086</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50980758624894</v>
+        <v>43.43799143092114</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84643672974775</v>
+        <v>99.84854137832272</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.51091789406023</v>
+        <v>84.21722248206414</v>
       </c>
       <c r="C6" t="n">
-        <v>42.56473522214077</v>
+        <v>41.33453128407344</v>
       </c>
       <c r="D6" t="n">
-        <v>2.104700117392648</v>
+        <v>2.047430625957128</v>
       </c>
       <c r="E6" t="n">
-        <v>7.687982784182458</v>
+        <v>7.413631930353777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469969829865799</v>
+        <v>0.7468261965999528</v>
       </c>
       <c r="G6" t="n">
-        <v>32.08896367712486</v>
+        <v>31.18879315417539</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36186121738267</v>
+        <v>34.35400504359782</v>
       </c>
       <c r="I6" t="n">
-        <v>3.851681971324887</v>
+        <v>3.798871802630369</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668731143666124</v>
+        <v>4.667663728749704</v>
       </c>
       <c r="K6" t="n">
-        <v>14.48908210593978</v>
+        <v>15.78277751793589</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81798575268752</v>
+        <v>42.75625225156943</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87180308076806</v>
+        <v>99.87356105357874</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84.19886304351571</v>
+        <v>82.4960802163928</v>
       </c>
       <c r="C7" t="n">
-        <v>41.8515445404927</v>
+        <v>40.20316072511358</v>
       </c>
       <c r="D7" t="n">
-        <v>2.04135869068118</v>
+        <v>1.963252313314203</v>
       </c>
       <c r="E7" t="n">
-        <v>7.992247661601581</v>
+        <v>7.637123812830299</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479473968176278</v>
+        <v>0.7477827170224784</v>
       </c>
       <c r="G7" t="n">
-        <v>31.12323904766099</v>
+        <v>29.90649330586655</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40558025361087</v>
+        <v>34.398004983034</v>
       </c>
       <c r="I7" t="n">
-        <v>3.213818763033292</v>
+        <v>3.169781102934776</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674671230110173</v>
+        <v>4.67364198139049</v>
       </c>
       <c r="K7" t="n">
-        <v>15.8011369564843</v>
+        <v>17.50391978360722</v>
       </c>
       <c r="L7" t="n">
-        <v>42.24032733715286</v>
+        <v>42.18739527453949</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89300883412986</v>
+        <v>99.89447578326028</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.91694031611677</v>
+        <v>87.40632273792963</v>
       </c>
       <c r="C8" t="n">
-        <v>44.11291730668393</v>
+        <v>42.54282746992848</v>
       </c>
       <c r="D8" t="n">
-        <v>2.045606433035101</v>
+        <v>1.967457817456477</v>
       </c>
       <c r="E8" t="n">
-        <v>9.792394421486073</v>
+        <v>9.494258001271749</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495037562416091</v>
+        <v>0.7493845505171504</v>
       </c>
       <c r="G8" t="n">
-        <v>31.61720465196202</v>
+        <v>30.42285855431007</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47717278711401</v>
+        <v>34.47168932378891</v>
       </c>
       <c r="I8" t="n">
-        <v>5.550659789767885</v>
+        <v>5.617021049853073</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684398476510056</v>
+        <v>4.683653440732189</v>
       </c>
       <c r="K8" t="n">
-        <v>11.08305968388326</v>
+        <v>12.59367726207039</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61938521828083</v>
+        <v>44.67666145175673</v>
       </c>
       <c r="M8" t="n">
-        <v>99.815362208848</v>
+        <v>99.8131661837556</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.01279916187116</v>
+        <v>85.32170202237948</v>
       </c>
       <c r="C9" t="n">
-        <v>43.0714930792803</v>
+        <v>41.32948002048495</v>
       </c>
       <c r="D9" t="n">
-        <v>1.959443159024967</v>
+        <v>1.872961343290614</v>
       </c>
       <c r="E9" t="n">
-        <v>10.15222106947434</v>
+        <v>9.819822398694543</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508342199312097</v>
+        <v>0.7507574656750092</v>
       </c>
       <c r="G9" t="n">
-        <v>30.28545196294671</v>
+        <v>28.96165677304613</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53837411683564</v>
+        <v>34.53484342105041</v>
       </c>
       <c r="I9" t="n">
-        <v>4.633760759088212</v>
+        <v>4.689426460153987</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692713874570059</v>
+        <v>4.692234160468806</v>
       </c>
       <c r="K9" t="n">
-        <v>12.98720083812886</v>
+        <v>14.67829797762048</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78712108843064</v>
+        <v>43.83619363939866</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8458150058398</v>
+        <v>99.8439716375041</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.8992877123468</v>
+        <v>83.07864545021198</v>
       </c>
       <c r="C10" t="n">
-        <v>41.67801684505959</v>
+        <v>39.81345063911569</v>
       </c>
       <c r="D10" t="n">
-        <v>1.86459111618071</v>
+        <v>1.772402115091702</v>
       </c>
       <c r="E10" t="n">
-        <v>10.30533097483029</v>
+        <v>9.944928526105146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519742860785252</v>
+        <v>0.7519364525245965</v>
       </c>
       <c r="G10" t="n">
-        <v>28.81940433920419</v>
+        <v>27.40670644644593</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59081715961216</v>
+        <v>34.58907681613142</v>
       </c>
       <c r="I10" t="n">
-        <v>3.867330548450147</v>
+        <v>3.913992265634446</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699839287990782</v>
+        <v>4.699602828278727</v>
       </c>
       <c r="K10" t="n">
-        <v>15.1007122876532</v>
+        <v>16.92135454978803</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09255529064588</v>
+        <v>43.13493296498088</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87128442335866</v>
+        <v>99.8697381538846</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.59730087186894</v>
+        <v>80.64904617178681</v>
       </c>
       <c r="C11" t="n">
-        <v>39.97644311865615</v>
+        <v>37.98998429863589</v>
       </c>
       <c r="D11" t="n">
-        <v>1.762166353438307</v>
+        <v>1.664580099266271</v>
       </c>
       <c r="E11" t="n">
-        <v>10.27707256148678</v>
+        <v>9.884284256563161</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529535756672237</v>
+        <v>0.7529514973656483</v>
       </c>
       <c r="G11" t="n">
-        <v>27.23631160310522</v>
+        <v>25.73945141948003</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63586448069228</v>
+        <v>34.6357688788198</v>
       </c>
       <c r="I11" t="n">
-        <v>3.226972449558983</v>
+        <v>3.266063161756591</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705959847920147</v>
+        <v>4.705946858535301</v>
       </c>
       <c r="K11" t="n">
-        <v>17.40269912813105</v>
+        <v>19.35095382821319</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51343190464473</v>
+        <v>42.55033986577219</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89257415143193</v>
+        <v>99.89127799262127</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.2735844106586</v>
+        <v>78.14423457145907</v>
       </c>
       <c r="C12" t="n">
-        <v>38.15297825048147</v>
+        <v>35.99007555592465</v>
       </c>
       <c r="D12" t="n">
-        <v>1.659762131426228</v>
+        <v>1.554568139668194</v>
       </c>
       <c r="E12" t="n">
-        <v>10.12853591187917</v>
+        <v>9.685179876201623</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537953070711414</v>
+        <v>0.7538266758629941</v>
       </c>
       <c r="G12" t="n">
-        <v>25.65353634766325</v>
+        <v>24.03833322703938</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6745841252725</v>
+        <v>34.67602708969771</v>
       </c>
       <c r="I12" t="n">
-        <v>2.692149918151669</v>
+        <v>2.724882838845431</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711220669194633</v>
+        <v>4.711416724143712</v>
       </c>
       <c r="K12" t="n">
-        <v>19.72641558934141</v>
+        <v>21.85576542854095</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03096803657825</v>
+        <v>42.06343503881893</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91036187640113</v>
+        <v>99.90927602328453</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.93113490444179</v>
+        <v>75.66999295658307</v>
       </c>
       <c r="C13" t="n">
-        <v>36.22708990267741</v>
+        <v>33.93612225373585</v>
       </c>
       <c r="D13" t="n">
-        <v>1.557417978962265</v>
+        <v>1.446985303923444</v>
       </c>
       <c r="E13" t="n">
-        <v>9.878259596760682</v>
+        <v>9.393758450078607</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754519336323955</v>
+        <v>0.7545814687083834</v>
       </c>
       <c r="G13" t="n">
-        <v>24.07168953630782</v>
+        <v>22.37477664875126</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70788947090193</v>
+        <v>34.71074756058562</v>
       </c>
       <c r="I13" t="n">
-        <v>2.245613133160432</v>
+        <v>2.273009345108346</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715745852024718</v>
+        <v>4.716134179427395</v>
       </c>
       <c r="K13" t="n">
-        <v>22.06886509555819</v>
+        <v>24.33000704341694</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62926305959353</v>
+        <v>41.65817951287928</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92521805782913</v>
+        <v>99.92430881003207</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.47958981347034</v>
+        <v>82.8959522267039</v>
       </c>
       <c r="C14" t="n">
-        <v>40.25765520260055</v>
+        <v>38.40723230439097</v>
       </c>
       <c r="D14" t="n">
-        <v>1.559231557387984</v>
+        <v>1.448728826087726</v>
       </c>
       <c r="E14" t="n">
-        <v>12.13590996330004</v>
+        <v>11.87602618497807</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553979572263906</v>
+        <v>0.7554906897708795</v>
       </c>
       <c r="G14" t="n">
-        <v>25.8539948643466</v>
+        <v>24.37326479353305</v>
       </c>
       <c r="H14" t="n">
-        <v>36.50258041602847</v>
+        <v>36.72409973933127</v>
       </c>
       <c r="I14" t="n">
-        <v>2.951237822515923</v>
+        <v>2.996525181934914</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72123723266494</v>
+        <v>4.721816811067996</v>
       </c>
       <c r="K14" t="n">
-        <v>15.52041018652965</v>
+        <v>17.1040477732961</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12367443856031</v>
+        <v>44.38895595859942</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90173982769052</v>
+        <v>99.90023603628649</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.73290196205133</v>
+        <v>82.07202046591478</v>
       </c>
       <c r="C15" t="n">
-        <v>39.96774063285811</v>
+        <v>38.0457627866271</v>
       </c>
       <c r="D15" t="n">
-        <v>1.531292473702939</v>
+        <v>1.418503897016115</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32874855772039</v>
+        <v>12.04486240664793</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561382555661071</v>
+        <v>0.7562576804817789</v>
       </c>
       <c r="G15" t="n">
-        <v>25.39073017304073</v>
+        <v>23.86476369494061</v>
       </c>
       <c r="H15" t="n">
-        <v>36.53835334792331</v>
+        <v>36.76138285049012</v>
       </c>
       <c r="I15" t="n">
-        <v>2.461775056809691</v>
+        <v>2.499639433327101</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725864097288169</v>
+        <v>4.726610503011117</v>
       </c>
       <c r="K15" t="n">
-        <v>16.26709803794865</v>
+        <v>17.92797953408524</v>
       </c>
       <c r="L15" t="n">
-        <v>43.68318250079002</v>
+        <v>43.94302086867835</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91802117159678</v>
+        <v>99.91676318939069</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.43390409310841</v>
+        <v>79.57579930066568</v>
       </c>
       <c r="C16" t="n">
-        <v>38.04982479342193</v>
+        <v>35.93533865735502</v>
       </c>
       <c r="D16" t="n">
-        <v>1.442813120778152</v>
+        <v>1.324801119697657</v>
       </c>
       <c r="E16" t="n">
-        <v>11.95858376951052</v>
+        <v>11.59668461622452</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567737425580239</v>
+        <v>0.7569181347747335</v>
       </c>
       <c r="G16" t="n">
-        <v>23.92363266255279</v>
+        <v>22.28831780503606</v>
       </c>
       <c r="H16" t="n">
-        <v>36.56906155252443</v>
+        <v>36.79348726905693</v>
       </c>
       <c r="I16" t="n">
-        <v>2.053203354196849</v>
+        <v>2.084852013533707</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729835890987649</v>
+        <v>4.730738342342083</v>
       </c>
       <c r="K16" t="n">
-        <v>18.56609590689158</v>
+        <v>20.4242006993343</v>
       </c>
       <c r="L16" t="n">
-        <v>43.31569665921955</v>
+        <v>43.57102621460716</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93161735953305</v>
+        <v>99.93056557129648</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.04077964803437</v>
+        <v>81.41527052168182</v>
       </c>
       <c r="C17" t="n">
-        <v>39.21645489979594</v>
+        <v>37.25829379600672</v>
       </c>
       <c r="D17" t="n">
-        <v>1.444007847220924</v>
+        <v>1.325936554606719</v>
       </c>
       <c r="E17" t="n">
-        <v>12.70818721375566</v>
+        <v>12.4274077779677</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574003916981021</v>
+        <v>0.7575668595234879</v>
       </c>
       <c r="G17" t="n">
-        <v>24.33933276953966</v>
+        <v>22.77931522141576</v>
       </c>
       <c r="H17" t="n">
-        <v>36.9952327510598</v>
+        <v>37.29691649540903</v>
       </c>
       <c r="I17" t="n">
-        <v>2.062866226647085</v>
+        <v>2.093334740737337</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733752448113138</v>
+        <v>4.734792872021798</v>
       </c>
       <c r="K17" t="n">
-        <v>16.95922035196561</v>
+        <v>18.58472947831818</v>
       </c>
       <c r="L17" t="n">
-        <v>43.75561943236026</v>
+        <v>44.08725865360003</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93129468412182</v>
+        <v>99.93028192792492</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.8245529280365</v>
+        <v>79.02312443055996</v>
       </c>
       <c r="C18" t="n">
-        <v>37.31921070036191</v>
+        <v>35.18882125860532</v>
       </c>
       <c r="D18" t="n">
-        <v>1.36183169860134</v>
+        <v>1.240027139723598</v>
       </c>
       <c r="E18" t="n">
-        <v>12.27169732247049</v>
+        <v>11.91317245060795</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579377435974827</v>
+        <v>0.7581247162049196</v>
       </c>
       <c r="G18" t="n">
-        <v>22.95422074897792</v>
+        <v>21.30340927756731</v>
       </c>
       <c r="H18" t="n">
-        <v>37.02147971211858</v>
+        <v>37.32438117895769</v>
       </c>
       <c r="I18" t="n">
-        <v>1.720274804786433</v>
+        <v>1.745730191217739</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737110897484266</v>
+        <v>4.738279476280747</v>
       </c>
       <c r="K18" t="n">
-        <v>19.17544707196349</v>
+        <v>20.97687556944005</v>
       </c>
       <c r="L18" t="n">
-        <v>43.44804038804551</v>
+        <v>43.77615498471194</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94269816037091</v>
+        <v>99.94185181275731</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.95650142541852</v>
+        <v>78.09696328132759</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71656306724957</v>
+        <v>34.52942025916365</v>
       </c>
       <c r="D19" t="n">
-        <v>1.330317029945471</v>
+        <v>1.207379396713753</v>
       </c>
       <c r="E19" t="n">
-        <v>12.22678321163827</v>
+        <v>11.84239341410007</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583909903593101</v>
+        <v>0.7585962549755515</v>
       </c>
       <c r="G19" t="n">
-        <v>22.42302833959232</v>
+        <v>20.74252781856747</v>
       </c>
       <c r="H19" t="n">
-        <v>37.04361855655444</v>
+        <v>37.34759621526968</v>
       </c>
       <c r="I19" t="n">
-        <v>1.434419607583019</v>
+        <v>1.457243588103863</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739943689745687</v>
+        <v>4.741226593597196</v>
       </c>
       <c r="K19" t="n">
-        <v>20.04349857458148</v>
+        <v>21.9030367186724</v>
       </c>
       <c r="L19" t="n">
-        <v>43.19215294692487</v>
+        <v>43.51899842968248</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95221458875592</v>
+        <v>99.95145540751852</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.53852555219792</v>
+        <v>75.58397386529001</v>
       </c>
       <c r="C20" t="n">
-        <v>34.51976864381241</v>
+        <v>32.24030241111146</v>
       </c>
       <c r="D20" t="n">
-        <v>1.241553614288695</v>
+        <v>1.118190582204073</v>
       </c>
       <c r="E20" t="n">
-        <v>11.61029674938037</v>
+        <v>11.17010216352861</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587809077169282</v>
+        <v>0.7590027388055058</v>
       </c>
       <c r="G20" t="n">
-        <v>20.92688528497587</v>
+        <v>19.21028246875661</v>
       </c>
       <c r="H20" t="n">
-        <v>37.06266407535384</v>
+        <v>37.36760843369233</v>
       </c>
       <c r="I20" t="n">
-        <v>1.195964247251426</v>
+        <v>1.215020360768458</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742380673230801</v>
+        <v>4.743767117534411</v>
       </c>
       <c r="K20" t="n">
-        <v>22.46147444780207</v>
+        <v>24.41602613471</v>
       </c>
       <c r="L20" t="n">
-        <v>42.97891191928598</v>
+        <v>43.3031924656201</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96015501090046</v>
+        <v>99.95952101144155</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.16469584326444</v>
+        <v>81.76581335696017</v>
       </c>
       <c r="C21" t="n">
-        <v>37.9716786405104</v>
+        <v>36.08982815016218</v>
       </c>
       <c r="D21" t="n">
-        <v>1.242429477146779</v>
+        <v>1.118982156025371</v>
       </c>
       <c r="E21" t="n">
-        <v>13.4834525057927</v>
+        <v>13.24019735524203</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593161951236449</v>
+        <v>0.7595400413976524</v>
       </c>
       <c r="G21" t="n">
-        <v>22.51326785414551</v>
+        <v>20.99665680335172</v>
       </c>
       <c r="H21" t="n">
-        <v>38.66042974483111</v>
+        <v>39.16683644826595</v>
       </c>
       <c r="I21" t="n">
-        <v>1.760073846701903</v>
+        <v>1.736475293942127</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74572621952278</v>
+        <v>4.747125258735327</v>
       </c>
       <c r="K21" t="n">
-        <v>16.83530415673558</v>
+        <v>18.23418664303982</v>
       </c>
       <c r="L21" t="n">
-        <v>45.13438943390857</v>
+        <v>45.61814364338967</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94137223115455</v>
+        <v>99.94215843659167</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_83_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.59827330284922</v>
+        <v>45.26086270738119</v>
       </c>
       <c r="M2" t="n">
-        <v>100.058567484908</v>
+        <v>100.8288467021024</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.91679806951458</v>
+        <v>88.04809700748058</v>
       </c>
       <c r="C3" t="n">
-        <v>45.85056609033798</v>
+        <v>45.90778316466456</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228506117191486</v>
+        <v>2.22879977950466</v>
       </c>
       <c r="E3" t="n">
-        <v>5.655795340565724</v>
+        <v>5.695663140575141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428353723971621</v>
+        <v>0.7429332598348868</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94714109026675</v>
+        <v>33.96562756798203</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17042713026945</v>
+        <v>34.17492995240479</v>
       </c>
       <c r="I3" t="n">
-        <v>6.529371941341743</v>
+        <v>6.59681043321102</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642721077482263</v>
+        <v>4.643332873968042</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0832019304854</v>
+        <v>11.95190299251943</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83183739920319</v>
+        <v>48.90352952530581</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7656054200266</v>
+        <v>106.7632156824898</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99932513121749</v>
+        <v>87.24833991734135</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56366219619926</v>
+        <v>42.74949032903681</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184182614409089</v>
+        <v>2.190849354013383</v>
       </c>
       <c r="E4" t="n">
-        <v>6.452057067312645</v>
+        <v>6.516833453921499</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443872302507726</v>
+        <v>0.7444969014697119</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27195505826018</v>
+        <v>33.38728489667682</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24181259153553</v>
+        <v>34.24685746760674</v>
       </c>
       <c r="I4" t="n">
-        <v>5.452510380381938</v>
+        <v>5.508912209467494</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652420189067328</v>
+        <v>4.6531056341857</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00067486878251</v>
+        <v>12.75166008265865</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25429149220317</v>
+        <v>44.31560485404868</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81862855718494</v>
+        <v>99.81675526574413</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.71100294647913</v>
+        <v>86.15177238398273</v>
       </c>
       <c r="C5" t="n">
-        <v>42.12155289388072</v>
+        <v>42.50802376848216</v>
       </c>
       <c r="D5" t="n">
-        <v>2.120785098149089</v>
+        <v>2.13757488420203</v>
       </c>
       <c r="E5" t="n">
-        <v>7.023415016174906</v>
+        <v>7.124853000891988</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457049542379405</v>
+        <v>0.7458216520592238</v>
       </c>
       <c r="G5" t="n">
-        <v>32.30621194782036</v>
+        <v>32.57541259790253</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30242789494525</v>
+        <v>34.30779599472429</v>
       </c>
       <c r="I5" t="n">
-        <v>4.551802071164457</v>
+        <v>4.598928928832515</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660655963987128</v>
+        <v>4.661385325370149</v>
       </c>
       <c r="K5" t="n">
-        <v>14.28899705352086</v>
+        <v>13.84822761601729</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43799143092114</v>
+        <v>43.49072327634869</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84854137832272</v>
+        <v>99.84697466084813</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.21722248206414</v>
+        <v>84.81726260031731</v>
       </c>
       <c r="C6" t="n">
-        <v>41.33453128407344</v>
+        <v>41.88789248039485</v>
       </c>
       <c r="D6" t="n">
-        <v>2.047430625957128</v>
+        <v>2.072513768864242</v>
       </c>
       <c r="E6" t="n">
-        <v>7.413631930353777</v>
+        <v>7.547698310529184</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468261965999528</v>
+        <v>0.7469466702403861</v>
       </c>
       <c r="G6" t="n">
-        <v>31.18879315417539</v>
+        <v>31.58391859604473</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35400504359782</v>
+        <v>34.35954683105776</v>
       </c>
       <c r="I6" t="n">
-        <v>3.798871802630369</v>
+        <v>3.838221734578595</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667663728749704</v>
+        <v>4.668416689002413</v>
       </c>
       <c r="K6" t="n">
-        <v>15.78277751793589</v>
+        <v>15.18273739968271</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75625225156943</v>
+        <v>42.80162209412153</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87356105357874</v>
+        <v>99.87225197419909</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.4960802163928</v>
+        <v>83.33720166286287</v>
       </c>
       <c r="C7" t="n">
-        <v>40.20316072511358</v>
+        <v>41.00410276024891</v>
       </c>
       <c r="D7" t="n">
-        <v>1.963252313314203</v>
+        <v>2.000628142877575</v>
       </c>
       <c r="E7" t="n">
-        <v>7.637123812830299</v>
+        <v>7.819673853567938</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477827170224784</v>
+        <v>0.7479034989794897</v>
       </c>
       <c r="G7" t="n">
-        <v>29.90649330586655</v>
+        <v>30.48842297449678</v>
       </c>
       <c r="H7" t="n">
-        <v>34.398004983034</v>
+        <v>34.40356095305653</v>
       </c>
       <c r="I7" t="n">
-        <v>3.169781102934776</v>
+        <v>3.20261537126274</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67364198139049</v>
+        <v>4.674396868621811</v>
       </c>
       <c r="K7" t="n">
-        <v>17.50391978360722</v>
+        <v>16.66279833713715</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18739527453949</v>
+        <v>42.226481632209</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89447578326028</v>
+        <v>99.89338272959505</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.40632273792963</v>
+        <v>88.06048728028065</v>
       </c>
       <c r="C8" t="n">
-        <v>42.54282746992848</v>
+        <v>43.25797616000192</v>
       </c>
       <c r="D8" t="n">
-        <v>1.967457817456477</v>
+        <v>2.004832279989062</v>
       </c>
       <c r="E8" t="n">
-        <v>9.494258001271749</v>
+        <v>9.615173700580995</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493845505171504</v>
+        <v>0.7494751497967916</v>
       </c>
       <c r="G8" t="n">
-        <v>30.42285855431007</v>
+        <v>30.97939771117014</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47168932378891</v>
+        <v>34.47585689065242</v>
       </c>
       <c r="I8" t="n">
-        <v>5.617021049853073</v>
+        <v>5.551531861861303</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683653440732189</v>
+        <v>4.684219686229948</v>
       </c>
       <c r="K8" t="n">
-        <v>12.59367726207039</v>
+        <v>11.93951271971934</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67666145175673</v>
+        <v>44.61784811064648</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8131661837556</v>
+        <v>99.81533699036774</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.32170202237948</v>
+        <v>85.96006135065342</v>
       </c>
       <c r="C9" t="n">
-        <v>41.32948002048495</v>
+        <v>42.01949900383492</v>
       </c>
       <c r="D9" t="n">
-        <v>1.872961343290614</v>
+        <v>1.909406496685188</v>
       </c>
       <c r="E9" t="n">
-        <v>9.819822398694543</v>
+        <v>9.929943541414584</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507574656750092</v>
+        <v>0.7508220972855365</v>
       </c>
       <c r="G9" t="n">
-        <v>28.96165677304613</v>
+        <v>29.50484379342955</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53484342105041</v>
+        <v>34.53781647513468</v>
       </c>
       <c r="I9" t="n">
-        <v>4.689426460153987</v>
+        <v>4.634590838669265</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692234160468806</v>
+        <v>4.692638108034604</v>
       </c>
       <c r="K9" t="n">
-        <v>14.67829797762048</v>
+        <v>14.03993864934659</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83619363939866</v>
+        <v>43.78635312843345</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8439716375041</v>
+        <v>99.84579078161495</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.07864545021198</v>
+        <v>83.69070313412199</v>
       </c>
       <c r="C10" t="n">
-        <v>39.81345063911569</v>
+        <v>40.46935088432083</v>
       </c>
       <c r="D10" t="n">
-        <v>1.772402115091702</v>
+        <v>1.807380542975107</v>
       </c>
       <c r="E10" t="n">
-        <v>9.944928526105146</v>
+        <v>10.04403842808658</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519364525245965</v>
+        <v>0.7519788414102851</v>
       </c>
       <c r="G10" t="n">
-        <v>27.40670644644593</v>
+        <v>27.92830164155275</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58907681613142</v>
+        <v>34.59102670487312</v>
       </c>
       <c r="I10" t="n">
-        <v>3.913992265634446</v>
+        <v>3.868109216409858</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699602828278727</v>
+        <v>4.699867758814283</v>
       </c>
       <c r="K10" t="n">
-        <v>16.92135454978803</v>
+        <v>16.30929686587801</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13493296498088</v>
+        <v>43.09261361539367</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8697381538846</v>
+        <v>99.87126136559252</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.64904617178681</v>
+        <v>81.15910851107931</v>
       </c>
       <c r="C11" t="n">
-        <v>37.98998429863589</v>
+        <v>38.53734222215006</v>
       </c>
       <c r="D11" t="n">
-        <v>1.664580099266271</v>
+        <v>1.694601748100071</v>
       </c>
       <c r="E11" t="n">
-        <v>9.884284256563161</v>
+        <v>9.955249749751905</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529514973656483</v>
+        <v>0.7529757146287358</v>
       </c>
       <c r="G11" t="n">
-        <v>25.73945141948003</v>
+        <v>26.18560267631098</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6357688788198</v>
+        <v>34.63688287292184</v>
       </c>
       <c r="I11" t="n">
-        <v>3.266063161756591</v>
+        <v>3.22769753293617</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705946858535301</v>
+        <v>4.706098216429599</v>
       </c>
       <c r="K11" t="n">
-        <v>19.35095382821319</v>
+        <v>18.8408914889207</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55033986577219</v>
+        <v>42.51431881069561</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89127799262127</v>
+        <v>99.89255252176638</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.14423457145907</v>
+        <v>78.52648153308557</v>
       </c>
       <c r="C12" t="n">
-        <v>35.99007555592465</v>
+        <v>36.40409423481687</v>
       </c>
       <c r="D12" t="n">
-        <v>1.554568139668194</v>
+        <v>1.578491999040888</v>
       </c>
       <c r="E12" t="n">
-        <v>9.685179876201623</v>
+        <v>9.72194541594453</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538266758629941</v>
+        <v>0.753836413637186</v>
       </c>
       <c r="G12" t="n">
-        <v>24.03833322703938</v>
+        <v>24.39143259527646</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67602708969771</v>
+        <v>34.67647502731055</v>
       </c>
       <c r="I12" t="n">
-        <v>2.724882838845431</v>
+        <v>2.692822496643527</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711416724143712</v>
+        <v>4.711477585232413</v>
       </c>
       <c r="K12" t="n">
-        <v>21.85576542854095</v>
+        <v>21.47351846691444</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06343503881893</v>
+        <v>42.03272903346492</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90927602328453</v>
+        <v>99.91034173519623</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.66999295658307</v>
+        <v>75.80274138747565</v>
       </c>
       <c r="C13" t="n">
-        <v>33.93612225373585</v>
+        <v>34.09596940282297</v>
       </c>
       <c r="D13" t="n">
-        <v>1.446985303923444</v>
+        <v>1.459473316508558</v>
       </c>
       <c r="E13" t="n">
-        <v>9.393758450078607</v>
+        <v>9.363280903263929</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545814687083834</v>
+        <v>0.7545810190529643</v>
       </c>
       <c r="G13" t="n">
-        <v>22.37477664875126</v>
+        <v>22.55231261599888</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71074756058562</v>
+        <v>34.71072687643635</v>
       </c>
       <c r="I13" t="n">
-        <v>2.273009345108346</v>
+        <v>2.246235287133948</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716134179427395</v>
+        <v>4.716131369081027</v>
       </c>
       <c r="K13" t="n">
-        <v>24.33000704341694</v>
+        <v>24.19725861252435</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65817951287928</v>
+        <v>41.6319713597459</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92430881003207</v>
+        <v>99.92519937509323</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.8959522267039</v>
+        <v>82.9237847741193</v>
       </c>
       <c r="C14" t="n">
-        <v>38.40723230439097</v>
+        <v>38.431310332834</v>
       </c>
       <c r="D14" t="n">
-        <v>1.448728826087726</v>
+        <v>1.461275564980154</v>
       </c>
       <c r="E14" t="n">
-        <v>11.87602618497807</v>
+        <v>11.78432910853285</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554906897708795</v>
+        <v>0.7555128226514954</v>
       </c>
       <c r="G14" t="n">
-        <v>24.37326479353305</v>
+        <v>24.47765021017904</v>
       </c>
       <c r="H14" t="n">
-        <v>36.72409973933127</v>
+        <v>36.65107843714132</v>
       </c>
       <c r="I14" t="n">
-        <v>2.996525181934914</v>
+        <v>3.071983489062589</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721816811067996</v>
+        <v>4.721955141571847</v>
       </c>
       <c r="K14" t="n">
-        <v>17.1040477732961</v>
+        <v>17.07621522588071</v>
       </c>
       <c r="L14" t="n">
-        <v>44.38895595859942</v>
+        <v>44.39020128490765</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90023603628649</v>
+        <v>99.89772684362235</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.07202046591478</v>
+        <v>81.87098798851615</v>
       </c>
       <c r="C15" t="n">
-        <v>38.0457627866271</v>
+        <v>37.85263529422131</v>
       </c>
       <c r="D15" t="n">
-        <v>1.418503897016115</v>
+        <v>1.421975762951952</v>
       </c>
       <c r="E15" t="n">
-        <v>12.04486240664793</v>
+        <v>11.89450883227096</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562576804817789</v>
+        <v>0.756301103688518</v>
       </c>
       <c r="G15" t="n">
-        <v>23.86476369494061</v>
+        <v>23.81934398072487</v>
       </c>
       <c r="H15" t="n">
-        <v>36.76138285049012</v>
+        <v>36.68931915159673</v>
       </c>
       <c r="I15" t="n">
-        <v>2.499639433327101</v>
+        <v>2.562657259229887</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726610503011117</v>
+        <v>4.726881898053238</v>
       </c>
       <c r="K15" t="n">
-        <v>17.92797953408524</v>
+        <v>18.12901201148386</v>
       </c>
       <c r="L15" t="n">
-        <v>43.94302086867835</v>
+        <v>43.93301981959866</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91676318939069</v>
+        <v>99.91466712530381</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.57579930066568</v>
+        <v>79.16908086175033</v>
       </c>
       <c r="C16" t="n">
-        <v>35.93533865735502</v>
+        <v>35.54614717220797</v>
       </c>
       <c r="D16" t="n">
-        <v>1.324801119697657</v>
+        <v>1.319703084997646</v>
       </c>
       <c r="E16" t="n">
-        <v>11.59668461622452</v>
+        <v>11.39526572040705</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569181347747335</v>
+        <v>0.7569817442523231</v>
       </c>
       <c r="G16" t="n">
-        <v>22.28831780503606</v>
+        <v>22.10618672481894</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79348726905693</v>
+        <v>36.72233806265105</v>
       </c>
       <c r="I16" t="n">
-        <v>2.084852013533707</v>
+        <v>2.137469623046301</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730738342342083</v>
+        <v>4.73113590157702</v>
       </c>
       <c r="K16" t="n">
-        <v>20.4242006993343</v>
+        <v>20.83091913824967</v>
       </c>
       <c r="L16" t="n">
-        <v>43.57102621460716</v>
+        <v>43.55174876567487</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93056557129648</v>
+        <v>99.92881507613251</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.41527052168182</v>
+        <v>80.79448199585542</v>
       </c>
       <c r="C17" t="n">
-        <v>37.25829379600672</v>
+        <v>36.7209669622347</v>
       </c>
       <c r="D17" t="n">
-        <v>1.325936554606719</v>
+        <v>1.320878250289643</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4274077779677</v>
+        <v>12.1572006957341</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575668595234879</v>
+        <v>0.7576558191125197</v>
       </c>
       <c r="G17" t="n">
-        <v>22.77931522141576</v>
+        <v>22.51793137493105</v>
       </c>
       <c r="H17" t="n">
-        <v>37.29691649540903</v>
+        <v>37.14709805988939</v>
       </c>
       <c r="I17" t="n">
-        <v>2.093334740737337</v>
+        <v>2.158368926445462</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734792872021798</v>
+        <v>4.735348869453249</v>
       </c>
       <c r="K17" t="n">
-        <v>18.58472947831818</v>
+        <v>19.20551800414457</v>
       </c>
       <c r="L17" t="n">
-        <v>44.08725865360003</v>
+        <v>44.00163341167289</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93028192792492</v>
+        <v>99.92811837805218</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.02312443055996</v>
+        <v>78.21503807771735</v>
       </c>
       <c r="C18" t="n">
-        <v>35.18882125860532</v>
+        <v>34.47399568393556</v>
       </c>
       <c r="D18" t="n">
-        <v>1.240027139723598</v>
+        <v>1.227165890003242</v>
       </c>
       <c r="E18" t="n">
-        <v>11.91317245060795</v>
+        <v>11.59468710177429</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581247162049196</v>
+        <v>0.7582370355812806</v>
       </c>
       <c r="G18" t="n">
-        <v>21.30340927756731</v>
+        <v>20.92035150907342</v>
       </c>
       <c r="H18" t="n">
-        <v>37.32438117895769</v>
+        <v>37.17559451515898</v>
       </c>
       <c r="I18" t="n">
-        <v>1.745730191217739</v>
+        <v>1.800020553743143</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738279476280747</v>
+        <v>4.738981472383005</v>
       </c>
       <c r="K18" t="n">
-        <v>20.97687556944005</v>
+        <v>21.78496192228264</v>
       </c>
       <c r="L18" t="n">
-        <v>43.77615498471194</v>
+        <v>43.68108770138052</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94185181275731</v>
+        <v>99.94004530759872</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.09696328132759</v>
+        <v>77.17399281213406</v>
       </c>
       <c r="C19" t="n">
-        <v>34.52942025916365</v>
+        <v>33.70939912553547</v>
       </c>
       <c r="D19" t="n">
-        <v>1.207379396713753</v>
+        <v>1.190075291513401</v>
       </c>
       <c r="E19" t="n">
-        <v>11.84239341410007</v>
+        <v>11.4944072539321</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585962549755515</v>
+        <v>0.7587286113358954</v>
       </c>
       <c r="G19" t="n">
-        <v>20.74252781856747</v>
+        <v>20.28804224721206</v>
       </c>
       <c r="H19" t="n">
-        <v>37.34759621526968</v>
+        <v>37.1996959769308</v>
       </c>
       <c r="I19" t="n">
-        <v>1.457243588103863</v>
+        <v>1.500989610360443</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741226593597196</v>
+        <v>4.742053820849348</v>
       </c>
       <c r="K19" t="n">
-        <v>21.9030367186724</v>
+        <v>22.82600718786595</v>
       </c>
       <c r="L19" t="n">
-        <v>43.51899842968248</v>
+        <v>43.41459311566128</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95145540751852</v>
+        <v>99.9499994290627</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.58397386529001</v>
+        <v>74.4830812596558</v>
       </c>
       <c r="C20" t="n">
-        <v>32.24030241111146</v>
+        <v>31.24881263073193</v>
       </c>
       <c r="D20" t="n">
-        <v>1.118190582204073</v>
+        <v>1.093564543615481</v>
       </c>
       <c r="E20" t="n">
-        <v>11.17010216352861</v>
+        <v>10.77084046237209</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590027388055058</v>
+        <v>0.7591535704909381</v>
       </c>
       <c r="G20" t="n">
-        <v>19.21028246875661</v>
+        <v>18.64275631898055</v>
       </c>
       <c r="H20" t="n">
-        <v>37.36760843369233</v>
+        <v>37.22053129424192</v>
       </c>
       <c r="I20" t="n">
-        <v>1.215020360768458</v>
+        <v>1.251525254386462</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743767117534411</v>
+        <v>4.744709815568365</v>
       </c>
       <c r="K20" t="n">
-        <v>24.41602613471</v>
+        <v>25.51691874034421</v>
       </c>
       <c r="L20" t="n">
-        <v>43.3031924656201</v>
+        <v>43.19257447308053</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95952101144155</v>
+        <v>99.95830584415665</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.76581335696017</v>
+        <v>80.79466852791923</v>
       </c>
       <c r="C21" t="n">
-        <v>36.08982815016218</v>
+        <v>35.14238670728054</v>
       </c>
       <c r="D21" t="n">
-        <v>1.118982156025371</v>
+        <v>1.094395805483634</v>
       </c>
       <c r="E21" t="n">
-        <v>13.24019735524203</v>
+        <v>12.87207498613961</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595400413976524</v>
+        <v>0.7597306332888363</v>
       </c>
       <c r="G21" t="n">
-        <v>20.99665680335172</v>
+        <v>20.4428984070726</v>
       </c>
       <c r="H21" t="n">
-        <v>39.16683644826595</v>
+        <v>39.03479508737846</v>
       </c>
       <c r="I21" t="n">
-        <v>1.736475293942127</v>
+        <v>1.842457150500865</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747125258735327</v>
+        <v>4.748316458055228</v>
       </c>
       <c r="K21" t="n">
-        <v>18.23418664303982</v>
+        <v>19.20533147208076</v>
       </c>
       <c r="L21" t="n">
-        <v>45.61814364338967</v>
+        <v>45.59091323099246</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94215843659167</v>
+        <v>99.93863141035376</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_83_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_83_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.26086270738119</v>
+        <v>43.74824367033635</v>
       </c>
       <c r="M2" t="n">
-        <v>100.8288467021024</v>
+        <v>95.16767271461896</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04809700748058</v>
+        <v>81.44637779265489</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90778316466456</v>
+        <v>43.20193334821046</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22879977950466</v>
+        <v>2.178362103923432</v>
       </c>
       <c r="E3" t="n">
-        <v>5.695663140575141</v>
+        <v>4.150629528863769</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429332598348868</v>
+        <v>0.7376114283893075</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96562756798203</v>
+        <v>32.76619664651496</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17492995240479</v>
+        <v>33.93012570590814</v>
       </c>
       <c r="I3" t="n">
-        <v>6.59681043321102</v>
+        <v>3.073380951622115</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643332873968042</v>
+        <v>4.610071427433172</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95190299251943</v>
+        <v>18.5536222073451</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90352952530581</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632156824898</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.24833991734135</v>
+        <v>88.50620595462362</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74949032903681</v>
+        <v>42.79673209603956</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190849354013383</v>
+        <v>2.184069083223518</v>
       </c>
       <c r="E4" t="n">
-        <v>6.516833453921499</v>
+        <v>6.529089972039254</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444969014697119</v>
+        <v>0.7395438587899937</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38728489667682</v>
+        <v>33.45615014835116</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24685746760674</v>
+        <v>34.01901750433971</v>
       </c>
       <c r="I4" t="n">
-        <v>5.508912209467494</v>
+        <v>6.956186270442546</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6531056341857</v>
+        <v>4.622149117437461</v>
       </c>
       <c r="K4" t="n">
-        <v>12.75166008265865</v>
+        <v>11.49379404537636</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31560485404868</v>
+        <v>45.47820686744721</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81675526574413</v>
+        <v>99.76873300886312</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.15177238398273</v>
+        <v>87.1734489240464</v>
       </c>
       <c r="C5" t="n">
-        <v>42.50802376848216</v>
+        <v>42.54223301383258</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13757488420203</v>
+        <v>2.119740371951095</v>
       </c>
       <c r="E5" t="n">
-        <v>7.124853000891988</v>
+        <v>7.305067989998123</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458216520592238</v>
+        <v>0.7411867625656878</v>
       </c>
       <c r="G5" t="n">
-        <v>32.57541259790253</v>
+        <v>32.47074586800503</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30779599472429</v>
+        <v>34.09459107802164</v>
       </c>
       <c r="I5" t="n">
-        <v>4.598928928832515</v>
+        <v>5.809699587469278</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661385325370149</v>
+        <v>4.632417266035549</v>
       </c>
       <c r="K5" t="n">
-        <v>13.84822761601729</v>
+        <v>12.82655107595361</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49072327634869</v>
+        <v>44.43798851381262</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84697466084813</v>
+        <v>99.8067726035988</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.81726260031731</v>
+        <v>85.64698002294975</v>
       </c>
       <c r="C6" t="n">
-        <v>41.88789248039485</v>
+        <v>41.91717481190511</v>
       </c>
       <c r="D6" t="n">
-        <v>2.072513768864242</v>
+        <v>2.046363275056266</v>
       </c>
       <c r="E6" t="n">
-        <v>7.547698310529184</v>
+        <v>7.860621189926269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469466702403861</v>
+        <v>0.7425859821272173</v>
       </c>
       <c r="G6" t="n">
-        <v>31.58391859604473</v>
+        <v>31.34673601409497</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35954683105776</v>
+        <v>34.15895517785199</v>
       </c>
       <c r="I6" t="n">
-        <v>3.838221734578595</v>
+        <v>4.850555995597911</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668416689002413</v>
+        <v>4.641162388295109</v>
       </c>
       <c r="K6" t="n">
-        <v>15.18273739968271</v>
+        <v>14.35301997705028</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80162209412153</v>
+        <v>43.56842466694825</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87225197419909</v>
+        <v>99.83861945590363</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.33720166286287</v>
+        <v>83.80163433319967</v>
       </c>
       <c r="C7" t="n">
-        <v>41.00410276024891</v>
+        <v>40.82464910417664</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000628142877575</v>
+        <v>1.9579741971445</v>
       </c>
       <c r="E7" t="n">
-        <v>7.819673853567938</v>
+        <v>8.195868668181042</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479034989794897</v>
+        <v>0.743781846996438</v>
       </c>
       <c r="G7" t="n">
-        <v>30.48842297449678</v>
+        <v>29.99276864886594</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40356095305653</v>
+        <v>34.21396496183615</v>
       </c>
       <c r="I7" t="n">
-        <v>3.20261537126274</v>
+        <v>4.048639466447887</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674396868621811</v>
+        <v>4.648636543727738</v>
       </c>
       <c r="K7" t="n">
-        <v>16.66279833713715</v>
+        <v>16.1983656668003</v>
       </c>
       <c r="L7" t="n">
-        <v>42.226481632209</v>
+        <v>42.8422475624787</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89338272959505</v>
+        <v>99.86526233345563</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.06048728028065</v>
+        <v>81.81374890387184</v>
       </c>
       <c r="C8" t="n">
-        <v>43.25797616000192</v>
+        <v>39.46481896886669</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004832279989062</v>
+        <v>1.863585546790721</v>
       </c>
       <c r="E8" t="n">
-        <v>9.615173700580995</v>
+        <v>8.36385302582579</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494751497967916</v>
+        <v>0.7448056662252469</v>
       </c>
       <c r="G8" t="n">
-        <v>30.97939771117014</v>
+        <v>28.54689823991557</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47585689065242</v>
+        <v>34.26106064636136</v>
       </c>
       <c r="I8" t="n">
-        <v>5.551531861861303</v>
+        <v>3.378510364845357</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684219686229948</v>
+        <v>4.655035413907794</v>
       </c>
       <c r="K8" t="n">
-        <v>11.93951271971934</v>
+        <v>18.18625109612817</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61784811064648</v>
+        <v>42.2364677276038</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81533699036774</v>
+        <v>99.88753779259865</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.96006135065342</v>
+        <v>79.54368959455383</v>
       </c>
       <c r="C9" t="n">
-        <v>42.01949900383492</v>
+        <v>37.71832072011229</v>
       </c>
       <c r="D9" t="n">
-        <v>1.909406496685188</v>
+        <v>1.756553596582254</v>
       </c>
       <c r="E9" t="n">
-        <v>9.929943541414584</v>
+        <v>8.353280797995653</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508220972855365</v>
+        <v>0.7456854433962965</v>
       </c>
       <c r="G9" t="n">
-        <v>29.50484379342955</v>
+        <v>26.90735440664074</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53781647513468</v>
+        <v>34.30153039622964</v>
       </c>
       <c r="I9" t="n">
-        <v>4.634590838669265</v>
+        <v>2.818750932482384</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692638108034604</v>
+        <v>4.660534021226854</v>
       </c>
       <c r="K9" t="n">
-        <v>14.03993864934659</v>
+        <v>20.45631040544618</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78635312843345</v>
+        <v>41.73152136430695</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84579078161495</v>
+        <v>99.90615248986541</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.69070313412199</v>
+        <v>84.78324437839389</v>
       </c>
       <c r="C10" t="n">
-        <v>40.46935088432083</v>
+        <v>41.36395301849034</v>
       </c>
       <c r="D10" t="n">
-        <v>1.807380542975107</v>
+        <v>1.758487010116411</v>
       </c>
       <c r="E10" t="n">
-        <v>10.04403842808658</v>
+        <v>10.39829562512589</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519788414102851</v>
+        <v>0.7465062087468621</v>
       </c>
       <c r="G10" t="n">
-        <v>27.92830164155275</v>
+        <v>28.50619288865358</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59102670487312</v>
+        <v>35.90850754247683</v>
       </c>
       <c r="I10" t="n">
-        <v>3.868109216409858</v>
+        <v>2.799591298606425</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699867758814283</v>
+        <v>4.66566380466789</v>
       </c>
       <c r="K10" t="n">
-        <v>16.30929686587801</v>
+        <v>15.21675562160612</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09261361539367</v>
+        <v>43.32607425269269</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87126136559252</v>
+        <v>99.90678289278914</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.15910851107931</v>
+        <v>84.15994257844464</v>
       </c>
       <c r="C11" t="n">
-        <v>38.53734222215006</v>
+        <v>41.0587177696549</v>
       </c>
       <c r="D11" t="n">
-        <v>1.694601748100071</v>
+        <v>1.724849618490429</v>
       </c>
       <c r="E11" t="n">
-        <v>9.955249749751905</v>
+        <v>10.63368122677943</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529757146287358</v>
+        <v>0.747220995588096</v>
       </c>
       <c r="G11" t="n">
-        <v>26.18560267631098</v>
+        <v>27.99228004411951</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63688287292184</v>
+        <v>35.97426095039666</v>
       </c>
       <c r="I11" t="n">
-        <v>3.22769753293617</v>
+        <v>2.417518520644913</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706098216429599</v>
+        <v>4.670131222425601</v>
       </c>
       <c r="K11" t="n">
-        <v>18.8408914889207</v>
+        <v>15.84005742155538</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51431881069561</v>
+        <v>43.02071794419511</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89255252176638</v>
+        <v>99.91949313540539</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.52648153308557</v>
+        <v>81.87360925488647</v>
       </c>
       <c r="C12" t="n">
-        <v>36.40409423481687</v>
+        <v>39.14746502262001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.578491999040888</v>
+        <v>1.628452897292729</v>
       </c>
       <c r="E12" t="n">
-        <v>9.72194541594453</v>
+        <v>10.37543845750918</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753836413637186</v>
+        <v>0.7478343744381416</v>
       </c>
       <c r="G12" t="n">
-        <v>24.39143259527646</v>
+        <v>26.42787466861641</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67647502731055</v>
+        <v>36.00379150553802</v>
       </c>
       <c r="I12" t="n">
-        <v>2.692822496643527</v>
+        <v>2.016252511253615</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711477585232413</v>
+        <v>4.673964840238386</v>
       </c>
       <c r="K12" t="n">
-        <v>21.47351846691444</v>
+        <v>18.12639074511352</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03272903346492</v>
+        <v>42.65899094002636</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91034173519623</v>
+        <v>99.93284670775989</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.80274138747565</v>
+        <v>82.96503781265174</v>
       </c>
       <c r="C13" t="n">
-        <v>34.09596940282297</v>
+        <v>40.07906072891987</v>
       </c>
       <c r="D13" t="n">
-        <v>1.459473316508558</v>
+        <v>1.629664885451407</v>
       </c>
       <c r="E13" t="n">
-        <v>9.363280903263929</v>
+        <v>10.9875936984972</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545810190529643</v>
+        <v>0.7483909557233468</v>
       </c>
       <c r="G13" t="n">
-        <v>22.55231261599888</v>
+        <v>26.7432403277481</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71072687643635</v>
+        <v>36.32628411186857</v>
       </c>
       <c r="I13" t="n">
-        <v>2.246235287133948</v>
+        <v>1.85242036009219</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716131369081027</v>
+        <v>4.677443473270919</v>
       </c>
       <c r="K13" t="n">
-        <v>24.19725861252435</v>
+        <v>17.03496218734826</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6319713597459</v>
+        <v>42.82427566013806</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92519937509323</v>
+        <v>99.93829857640618</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.9237847741193</v>
+        <v>80.60095007091728</v>
       </c>
       <c r="C14" t="n">
-        <v>38.431310332834</v>
+        <v>38.00208273125393</v>
       </c>
       <c r="D14" t="n">
-        <v>1.461275564980154</v>
+        <v>1.532761754485843</v>
       </c>
       <c r="E14" t="n">
-        <v>11.78432910853285</v>
+        <v>10.59169437848353</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555128226514954</v>
+        <v>0.7488690381267209</v>
       </c>
       <c r="G14" t="n">
-        <v>24.47765021017904</v>
+        <v>25.15303381163635</v>
       </c>
       <c r="H14" t="n">
-        <v>36.65107843714132</v>
+        <v>36.34948984021288</v>
       </c>
       <c r="I14" t="n">
-        <v>3.071983489062589</v>
+        <v>1.544669759679946</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721955141571847</v>
+        <v>4.680431488292007</v>
       </c>
       <c r="K14" t="n">
-        <v>17.07621522588071</v>
+        <v>19.39904992908274</v>
       </c>
       <c r="L14" t="n">
-        <v>44.39020128490765</v>
+        <v>42.54741121854966</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89772684362235</v>
+        <v>99.94854387888631</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.87098798851615</v>
+        <v>79.44668966008018</v>
       </c>
       <c r="C15" t="n">
-        <v>37.85263529422131</v>
+        <v>37.04669963273962</v>
       </c>
       <c r="D15" t="n">
-        <v>1.421975762951952</v>
+        <v>1.48422003109845</v>
       </c>
       <c r="E15" t="n">
-        <v>11.89450883227096</v>
+        <v>10.4773630517453</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756301103688518</v>
+        <v>0.7492858618058088</v>
       </c>
       <c r="G15" t="n">
-        <v>23.81934398072487</v>
+        <v>24.3564510380482</v>
       </c>
       <c r="H15" t="n">
-        <v>36.68931915159673</v>
+        <v>36.36972212024688</v>
       </c>
       <c r="I15" t="n">
-        <v>2.562657259229887</v>
+        <v>1.326610920849254</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726881898053238</v>
+        <v>4.683036636286307</v>
       </c>
       <c r="K15" t="n">
-        <v>18.12901201148386</v>
+        <v>20.5533103399198</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93301981959866</v>
+        <v>42.35579426286203</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91466712530381</v>
+        <v>99.95580423552146</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.16908086175033</v>
+        <v>76.66686121802833</v>
       </c>
       <c r="C16" t="n">
-        <v>35.54614717220797</v>
+        <v>34.47174305743049</v>
       </c>
       <c r="D16" t="n">
-        <v>1.319703084997646</v>
+        <v>1.371275055598827</v>
       </c>
       <c r="E16" t="n">
-        <v>11.39526572040705</v>
+        <v>9.864405273021395</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569817442523231</v>
+        <v>0.7496461829251592</v>
       </c>
       <c r="G16" t="n">
-        <v>22.10618672481894</v>
+        <v>22.50299352628412</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72233806265105</v>
+        <v>36.38721181230279</v>
       </c>
       <c r="I16" t="n">
-        <v>2.137469623046301</v>
+        <v>1.106040724613785</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73113590157702</v>
+        <v>4.685288643282247</v>
       </c>
       <c r="K16" t="n">
-        <v>20.83091913824967</v>
+        <v>23.33313878197169</v>
       </c>
       <c r="L16" t="n">
-        <v>43.55174876567487</v>
+        <v>42.1582678572409</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92881507613251</v>
+        <v>99.96314969664307</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.79448199585542</v>
+        <v>82.0515706612353</v>
       </c>
       <c r="C17" t="n">
-        <v>36.7209669622347</v>
+        <v>38.08634653831704</v>
       </c>
       <c r="D17" t="n">
-        <v>1.320878250289643</v>
+        <v>1.371916705799189</v>
       </c>
       <c r="E17" t="n">
-        <v>12.1572006957341</v>
+        <v>11.76486049958595</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576558191125197</v>
+        <v>0.7499969591035127</v>
       </c>
       <c r="G17" t="n">
-        <v>22.51793137493105</v>
+        <v>24.21739382532171</v>
       </c>
       <c r="H17" t="n">
-        <v>37.14709805988939</v>
+        <v>38.10810884692141</v>
       </c>
       <c r="I17" t="n">
-        <v>2.158368926445462</v>
+        <v>1.151812830106569</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735348869453249</v>
+        <v>4.687480994396957</v>
       </c>
       <c r="K17" t="n">
-        <v>19.20551800414457</v>
+        <v>17.9484293387647</v>
       </c>
       <c r="L17" t="n">
-        <v>44.00163341167289</v>
+        <v>43.92684831880986</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92811837805218</v>
+        <v>99.9616241958916</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.21503807771735</v>
+        <v>83.58578706856996</v>
       </c>
       <c r="C18" t="n">
-        <v>34.47399568393556</v>
+        <v>38.80615133429865</v>
       </c>
       <c r="D18" t="n">
-        <v>1.227165890003242</v>
+        <v>1.37296798481056</v>
       </c>
       <c r="E18" t="n">
-        <v>11.59468710177429</v>
+        <v>12.34897411626515</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582370355812806</v>
+        <v>0.7505716704240799</v>
       </c>
       <c r="G18" t="n">
-        <v>20.92035150907342</v>
+        <v>24.36337412933923</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17559451515898</v>
+        <v>38.13731051406671</v>
       </c>
       <c r="I18" t="n">
-        <v>1.800020553743143</v>
+        <v>1.921515713513718</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738981472383005</v>
+        <v>4.691072940150502</v>
       </c>
       <c r="K18" t="n">
-        <v>21.78496192228264</v>
+        <v>16.41421293143004</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68108770138052</v>
+        <v>44.71563425385349</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94004530759872</v>
+        <v>99.93599851958217</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.17399281213406</v>
+        <v>80.50243168879611</v>
       </c>
       <c r="C19" t="n">
-        <v>33.70939912553547</v>
+        <v>36.01940970349762</v>
       </c>
       <c r="D19" t="n">
-        <v>1.190075291513401</v>
+        <v>1.262650817893347</v>
       </c>
       <c r="E19" t="n">
-        <v>11.4944072539321</v>
+        <v>11.6237955845241</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587286113358954</v>
+        <v>0.7510696512878658</v>
       </c>
       <c r="G19" t="n">
-        <v>20.28804224721206</v>
+        <v>22.40579140328342</v>
       </c>
       <c r="H19" t="n">
-        <v>37.1996959769308</v>
+        <v>38.16261342860589</v>
       </c>
       <c r="I19" t="n">
-        <v>1.500989610360443</v>
+        <v>1.602325482652317</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742053820849348</v>
+        <v>4.694185320549163</v>
       </c>
       <c r="K19" t="n">
-        <v>22.82600718786595</v>
+        <v>19.49756831120391</v>
       </c>
       <c r="L19" t="n">
-        <v>43.41459311566128</v>
+        <v>44.42964654881197</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9499994290627</v>
+        <v>99.9466245635135</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.4830812596558</v>
+        <v>77.30409401790084</v>
       </c>
       <c r="C20" t="n">
-        <v>31.24881263073193</v>
+        <v>33.06751499201741</v>
       </c>
       <c r="D20" t="n">
-        <v>1.093564543615481</v>
+        <v>1.148885341147095</v>
       </c>
       <c r="E20" t="n">
-        <v>10.77084046237209</v>
+        <v>10.79915914214209</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591535704909381</v>
+        <v>0.7515023405140879</v>
       </c>
       <c r="G20" t="n">
-        <v>18.64275631898055</v>
+        <v>20.38701827555165</v>
       </c>
       <c r="H20" t="n">
-        <v>37.22053129424192</v>
+        <v>38.18459880858592</v>
       </c>
       <c r="I20" t="n">
-        <v>1.251525254386462</v>
+        <v>1.336040481746946</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744709815568365</v>
+        <v>4.696889628213051</v>
       </c>
       <c r="K20" t="n">
-        <v>25.51691874034421</v>
+        <v>22.69590598209917</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19257447308053</v>
+        <v>44.19206998469865</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95830584415665</v>
+        <v>99.95549095881522</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.79466852791923</v>
+        <v>74.32372397230242</v>
       </c>
       <c r="C21" t="n">
-        <v>35.14238670728054</v>
+        <v>30.29175623177695</v>
       </c>
       <c r="D21" t="n">
-        <v>1.094395805483634</v>
+        <v>1.043511957479276</v>
       </c>
       <c r="E21" t="n">
-        <v>12.87207498613961</v>
+        <v>9.994336516200107</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597306332888363</v>
+        <v>0.7518777773696147</v>
       </c>
       <c r="G21" t="n">
-        <v>20.4428984070726</v>
+        <v>18.51716318936209</v>
       </c>
       <c r="H21" t="n">
-        <v>39.03479508737846</v>
+        <v>38.20367513733886</v>
       </c>
       <c r="I21" t="n">
-        <v>1.842457150500865</v>
+        <v>1.113923285992405</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748316458055228</v>
+        <v>4.699236108560093</v>
       </c>
       <c r="K21" t="n">
-        <v>19.20533147208076</v>
+        <v>25.67627602769755</v>
       </c>
       <c r="L21" t="n">
-        <v>45.59091323099246</v>
+        <v>43.99485550492142</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93863141035376</v>
+        <v>99.96288776439593</v>
       </c>
     </row>
   </sheetData>
